--- a/แบบเก็บข้อมูล ประเด็น Challenge มะพร้าวน้ำหอม 15_5_20.xlsx
+++ b/แบบเก็บข้อมูล ประเด็น Challenge มะพร้าวน้ำหอม 15_5_20.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\coding+\coconut-data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\coding\coconut_doae\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38739812-A647-4FF7-B748-5B03C225A12F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FC9A2CD-FE71-4ADE-B9F7-D51A348F5722}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{3F84BCBA-BFC2-4333-A992-26699FEED3F5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3F84BCBA-BFC2-4333-A992-26699FEED3F5}"/>
   </bookViews>
   <sheets>
     <sheet name="ระดับจังหวัด " sheetId="1" r:id="rId1"/>
@@ -555,22 +555,22 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J31"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="24" x14ac:dyDescent="0.8"/>
+  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="24" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="6.4140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="7.4140625" style="6" customWidth="1"/>
-    <col min="3" max="3" width="8.33203125" style="6" customWidth="1"/>
+    <col min="1" max="1" width="6.375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="7.375" style="6" customWidth="1"/>
+    <col min="3" max="3" width="8.375" style="6" customWidth="1"/>
     <col min="4" max="4" width="15" style="1" customWidth="1"/>
-    <col min="5" max="5" width="14.83203125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="15.6640625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="15.1640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="14.875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="15.625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="15.125" style="1" customWidth="1"/>
     <col min="8" max="8" width="19.5" style="1" customWidth="1"/>
-    <col min="9" max="9" width="20.6640625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="20.625" style="1" customWidth="1"/>
     <col min="10" max="10" width="11.25" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="8.6640625" style="1"/>
+    <col min="11" max="16384" width="8.625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.8">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="8" t="s">
         <v>10</v>
       </c>
@@ -584,7 +584,7 @@
       <c r="I1" s="8"/>
       <c r="J1" s="8"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.8">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="8" t="s">
         <v>9</v>
       </c>
@@ -598,7 +598,7 @@
       <c r="I2" s="8"/>
       <c r="J2" s="8"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.8">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="8" t="s">
         <v>14</v>
       </c>
@@ -612,8 +612,8 @@
       <c r="I3" s="8"/>
       <c r="J3" s="8"/>
     </row>
-    <row r="4" spans="1:10" ht="8.5" customHeight="1" x14ac:dyDescent="0.8"/>
-    <row r="5" spans="1:10" ht="84.5" customHeight="1" x14ac:dyDescent="0.8">
+    <row r="4" spans="1:10" ht="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="5" spans="1:10" ht="84.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="4" t="s">
         <v>4</v>
       </c>
@@ -645,7 +645,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.8">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="3"/>
       <c r="B6" s="3">
         <v>1</v>
@@ -661,7 +661,7 @@
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.8">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
       <c r="C7" s="3">
@@ -675,7 +675,7 @@
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.8">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="3"/>
       <c r="B8" s="3">
         <v>2</v>
@@ -691,7 +691,7 @@
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.8">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="3"/>
       <c r="B9" s="3"/>
       <c r="C9" s="3">
@@ -705,7 +705,7 @@
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.8">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="3"/>
       <c r="B10" s="3">
         <v>3</v>
@@ -721,7 +721,7 @@
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.8">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3">
@@ -735,7 +735,7 @@
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.8">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="3"/>
       <c r="B12" s="3">
         <v>4</v>
@@ -751,7 +751,7 @@
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.8">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="3"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3">
@@ -765,7 +765,7 @@
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.8">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="3"/>
       <c r="B14" s="3">
         <v>5</v>
@@ -781,7 +781,7 @@
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.8">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="3"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3">
@@ -795,7 +795,7 @@
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.8">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="3"/>
       <c r="B16" s="3">
         <v>6</v>
@@ -811,7 +811,7 @@
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.8">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="3"/>
       <c r="B17" s="3"/>
       <c r="C17" s="3">
@@ -825,7 +825,7 @@
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.8">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="3"/>
       <c r="B18" s="3">
         <v>7</v>
@@ -841,7 +841,7 @@
       <c r="I18" s="2"/>
       <c r="J18" s="2"/>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.8">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="3"/>
       <c r="B19" s="3"/>
       <c r="C19" s="3">
@@ -855,7 +855,7 @@
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.8">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="3"/>
       <c r="B20" s="3">
         <v>8</v>
@@ -871,7 +871,7 @@
       <c r="I20" s="2"/>
       <c r="J20" s="2"/>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.8">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="3"/>
       <c r="B21" s="3"/>
       <c r="C21" s="3">
@@ -885,7 +885,7 @@
       <c r="I21" s="2"/>
       <c r="J21" s="2"/>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.8">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="3"/>
       <c r="B22" s="3">
         <v>9</v>
@@ -901,7 +901,7 @@
       <c r="I22" s="2"/>
       <c r="J22" s="2"/>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.8">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="3"/>
       <c r="B23" s="3"/>
       <c r="C23" s="3">
@@ -915,7 +915,7 @@
       <c r="I23" s="2"/>
       <c r="J23" s="2"/>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.8">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="3"/>
       <c r="B24" s="3">
         <v>10</v>
@@ -931,7 +931,7 @@
       <c r="I24" s="2"/>
       <c r="J24" s="2"/>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.8">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="3"/>
       <c r="B25" s="3"/>
       <c r="C25" s="3">
@@ -945,7 +945,7 @@
       <c r="I25" s="2"/>
       <c r="J25" s="2"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.8">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="10" t="s">
         <v>18</v>
       </c>
@@ -961,7 +961,7 @@
       <c r="I27" s="9"/>
       <c r="J27" s="9"/>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.8">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="11"/>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
@@ -975,7 +975,7 @@
       <c r="I28" s="7"/>
       <c r="J28" s="7"/>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.8">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="11"/>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
@@ -989,7 +989,7 @@
       <c r="I29" s="7"/>
       <c r="J29" s="7"/>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.8">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="11"/>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
@@ -1003,7 +1003,7 @@
       <c r="I30" s="7"/>
       <c r="J30" s="7"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.8">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="11"/>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
